--- a/Data/EXCEL/Transfer/dividend/20260225_0_4/00952-dividend-20260225_0_4.xlsx
+++ b/Data/EXCEL/Transfer/dividend/20260225_0_4/00952-dividend-20260225_0_4.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\workspaces\xls2xlxs\20260225_0_4\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Workspaces\xls2xlsx\transfer\20260225_0_4\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{1D3B8343-07AB-41F7-BD6B-3906F54E14AC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{9EFD413F-1171-4DA1-9652-EFBDB2DF5111}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="4140" yWindow="576" windowWidth="16656" windowHeight="10992" xr2:uid="{50E342F5-C932-4F7C-B943-5FE4454410FB}"/>
+    <workbookView xWindow="780" yWindow="780" windowWidth="22845" windowHeight="19530" xr2:uid="{79E991B6-C22A-47F7-82CC-7A821A90CAC4}"/>
   </bookViews>
   <sheets>
     <sheet name="00952-dividend-20260225_0_4" sheetId="2" r:id="rId1"/>
@@ -1525,20 +1525,20 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{63182CDF-8382-40A6-90C9-B5B1E214EC87}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2805947C-79A2-4147-BCE8-3E1A8C9B076F}">
   <dimension ref="A1:R17"/>
-  <sheetFormatPr defaultRowHeight="16.2" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="5.109375" customWidth="1"/>
-    <col min="2" max="2" width="8.77734375" customWidth="1"/>
-    <col min="3" max="3" width="8.33203125" customWidth="1"/>
-    <col min="4" max="13" width="8" customWidth="1"/>
-    <col min="14" max="14" width="8.33203125" customWidth="1"/>
-    <col min="15" max="17" width="8" customWidth="1"/>
-    <col min="18" max="18" width="8.88671875" customWidth="1"/>
+    <col min="1" max="1" width="6.5" customWidth="1"/>
+    <col min="2" max="2" width="11" customWidth="1"/>
+    <col min="3" max="3" width="11.5" customWidth="1"/>
+    <col min="4" max="13" width="10" customWidth="1"/>
+    <col min="14" max="14" width="10.5" customWidth="1"/>
+    <col min="15" max="17" width="10" customWidth="1"/>
+    <col min="18" max="18" width="10.25" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:18" s="1" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:18" s="1" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A1" s="23" t="s">
         <v>0</v>
       </c>
@@ -1566,7 +1566,7 @@
       <c r="Q1" s="32"/>
       <c r="R1" s="24"/>
     </row>
-    <row r="2" spans="1:18" s="3" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:18" s="3" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A2" s="25" t="s">
         <v>1</v>
       </c>
@@ -1596,7 +1596,7 @@
       <c r="Q2" s="34"/>
       <c r="R2" s="35"/>
     </row>
-    <row r="3" spans="1:18" s="3" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:18" s="3" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A3" s="25" t="s">
         <v>2</v>
       </c>
@@ -1642,7 +1642,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="4" spans="1:18" s="3" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:18" s="3" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A4" s="27"/>
       <c r="B4" s="28"/>
       <c r="C4" s="7"/>
@@ -1692,7 +1692,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="5" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A5" s="39">
         <v>2026</v>
       </c>
@@ -1746,7 +1746,7 @@
         <v>4.67</v>
       </c>
     </row>
-    <row r="6" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A6" s="41"/>
       <c r="B6" s="42"/>
       <c r="C6" s="44"/>
@@ -1772,7 +1772,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="7" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A7" s="11" t="s">
         <v>26</v>
       </c>
@@ -1828,7 +1828,7 @@
         <v>0.38</v>
       </c>
     </row>
-    <row r="8" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A8" s="11" t="s">
         <v>26</v>
       </c>
@@ -1884,7 +1884,7 @@
         <v>0.4</v>
       </c>
     </row>
-    <row r="9" spans="1:18" s="17" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:18" s="17" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A9" s="49">
         <v>2025</v>
       </c>
@@ -1938,7 +1938,7 @@
         <v>1.66</v>
       </c>
     </row>
-    <row r="10" spans="1:18" s="17" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:18" s="17" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A10" s="19" t="s">
         <v>26</v>
       </c>
@@ -1994,7 +1994,7 @@
         <v>0.26</v>
       </c>
     </row>
-    <row r="11" spans="1:18" s="17" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:18" s="17" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A11" s="19" t="s">
         <v>26</v>
       </c>
@@ -2050,7 +2050,7 @@
         <v>0.26</v>
       </c>
     </row>
-    <row r="12" spans="1:18" s="17" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:18" s="17" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A12" s="19" t="s">
         <v>26</v>
       </c>
@@ -2106,7 +2106,7 @@
         <v>0.26</v>
       </c>
     </row>
-    <row r="13" spans="1:18" s="17" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:18" s="17" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A13" s="19" t="s">
         <v>26</v>
       </c>
@@ -2162,7 +2162,7 @@
         <v>0.27</v>
       </c>
     </row>
-    <row r="14" spans="1:18" s="17" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:18" s="17" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A14" s="19" t="s">
         <v>26</v>
       </c>
@@ -2218,7 +2218,7 @@
         <v>0.19</v>
       </c>
     </row>
-    <row r="15" spans="1:18" s="17" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:18" s="17" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A15" s="19" t="s">
         <v>26</v>
       </c>
@@ -2274,7 +2274,7 @@
         <v>0.21</v>
       </c>
     </row>
-    <row r="16" spans="1:18" s="17" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:18" s="17" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A16" s="19" t="s">
         <v>26</v>
       </c>
@@ -2330,7 +2330,7 @@
         <v>0.21</v>
       </c>
     </row>
-    <row r="17" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A17" s="51" t="s">
         <v>46</v>
       </c>
